--- a/www/terminologies/ASS-X08-TranscoSavoirFaireR01-SavoirFaire.xlsx
+++ b/www/terminologies/ASS-X08-TranscoSavoirFaireR01-SavoirFaire.xlsx
@@ -105,7 +105,7 @@
     <t>Target</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/TRE_R01-EnsembleSavoirFaire-CISIS/FHIR/TRE-R01-EnsembleSavoirFaire-CISIS|20241213120000</t>
+    <t>https://mos.esante.gouv.fr/NOS/TRE_R01-EnsembleSavoirFaire-CISIS/FHIR/TRE-R01-EnsembleSavoirFaire-CISIS|20260202120000</t>
   </si>
   <si>
     <t/>

--- a/www/terminologies/ASS-X08-TranscoSavoirFaireR01-SavoirFaire.xlsx
+++ b/www/terminologies/ASS-X08-TranscoSavoirFaireR01-SavoirFaire.xlsx
@@ -105,13 +105,13 @@
     <t>Target</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/TRE_R01-EnsembleSavoirFaire-CISIS/FHIR/TRE-R01-EnsembleSavoirFaire-CISIS|20260202120000</t>
+    <t>https://mos.esante.gouv.fr/NOS/TRE_R01-EnsembleSavoirFaire-CISIS/FHIR/TRE-R01-EnsembleSavoirFaire-CISIS</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/TRE_R38-SpecialiteOrdinale/FHIR/TRE-R38-SpecialiteOrdinale|20240531120000</t>
+    <t>https://mos.esante.gouv.fr/NOS/TRE_R38-SpecialiteOrdinale/FHIR/TRE-R38-SpecialiteOrdinale</t>
   </si>
   <si>
     <t>SCD01</t>
@@ -426,7 +426,7 @@
     <t>SM95</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/TRE_R39-Competence/FHIR/TRE-R39-Competence|20240628120000</t>
+    <t>https://mos.esante.gouv.fr/NOS/TRE_R39-Competence/FHIR/TRE-R39-Competence</t>
   </si>
   <si>
     <t>C01</t>
@@ -558,7 +558,7 @@
     <t>C83</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/TRE_R40-CompetenceExclusive/FHIR/TRE-R40-CompetenceExclusive|20231215120000</t>
+    <t>https://mos.esante.gouv.fr/NOS/TRE_R40-CompetenceExclusive/FHIR/TRE-R40-CompetenceExclusive</t>
   </si>
   <si>
     <t>CEX22</t>
@@ -573,7 +573,7 @@
     <t>CEX64</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/TRE_R42-DESCnonQualifiant/FHIR/TRE-R42-DESCnonQualifiant|20240628120000</t>
+    <t>https://mos.esante.gouv.fr/NOS/TRE_R42-DESCnonQualifiant/FHIR/TRE-R42-DESCnonQualifiant</t>
   </si>
   <si>
     <t>DSM200</t>
@@ -699,7 +699,7 @@
     <t>DSM240</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/TRE_R43-CapaciteSavoirFaire/FHIR/TRE-R43-CapaciteSavoirFaire|20231215120000</t>
+    <t>https://mos.esante.gouv.fr/NOS/TRE_R43-CapaciteSavoirFaire/FHIR/TRE-R43-CapaciteSavoirFaire</t>
   </si>
   <si>
     <t>CAPA01</t>
@@ -750,13 +750,13 @@
     <t>CAPA16</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/TRE_R44-QualificationPAC/FHIR/TRE-R44-QualificationPAC|20231215120000</t>
+    <t>https://mos.esante.gouv.fr/NOS/TRE_R44-QualificationPAC/FHIR/TRE-R44-QualificationPAC</t>
   </si>
   <si>
     <t>PAC00</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/TRE_R46-SpecialiteConcoursHospitalier/FHIR/TRE-R46-SpecialiteConcoursHospitalier|20231215120000</t>
+    <t>https://mos.esante.gouv.fr/NOS/TRE_R46-SpecialiteConcoursHospitalier/FHIR/TRE-R46-SpecialiteConcoursHospitalier</t>
   </si>
   <si>
     <t>SCH01</t>
